--- a/group-project/group-project-rubric.xlsx
+++ b/group-project/group-project-rubric.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/T7/Dropbox/LBS/2025-2026/E628-new/rubrics/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/T7/Dropbox/LBS/01_websites_github_repos/e628-shared/group-project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{73531F80-A4AE-B84E-881D-5422308DF649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{160B0ED0-4156-B14B-9AD1-9D699EDB4155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="67200" windowHeight="35520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -350,13 +350,6 @@
     <t>Exemplary (9-10)</t>
   </si>
   <si>
-    <t>• Notebook and app tell a compelling, logical narrative: business question → data → insights → recommendations
-• Visualisations are polished, consistently styled and publication-ready
-• Business implications stated clearly and specifically for every finding
-• 10-minute presentation is well-paced, rehearsed and engages the audience
-• All team members contribute meaningfully to the presentation</t>
-  </si>
-  <si>
     <t>• Clear introduction, body and conclusion in the notebook
 • Consistent colour theme and font across all charts
 • 'So what?' stated explicitly for every key finding
@@ -584,12 +577,17 @@
   <si>
     <t>Final Adjusted Individual Score:</t>
   </si>
+  <si>
+    <t>• Notebook and app tell a compelling, logical narrative: business question → data → insights → recommendations
+• Visualisations are polished, consistently styled and publication-ready
+• Business implications stated clearly and specifically for every finding</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -637,6 +635,12 @@
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -704,7 +708,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -764,15 +768,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -790,6 +794,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1103,7 +1110,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="20"/>
@@ -1145,7 +1152,7 @@
       <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="23" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -1221,7 +1228,7 @@
       <c r="A14" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="23" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1297,7 +1304,7 @@
       <c r="A22" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="23" t="s">
         <v>31</v>
       </c>
       <c r="C22" s="3" t="s">
@@ -1373,7 +1380,7 @@
       <c r="A30" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B30" s="21" t="s">
+      <c r="B30" s="23" t="s">
         <v>44</v>
       </c>
       <c r="C30" s="3" t="s">
@@ -1449,7 +1456,7 @@
       <c r="A38" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="B38" s="21" t="s">
+      <c r="B38" s="23" t="s">
         <v>58</v>
       </c>
       <c r="C38" s="3" t="s">
@@ -1457,21 +1464,21 @@
       </c>
       <c r="D38" s="4"/>
     </row>
-    <row r="39" spans="1:4" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" ht="96" x14ac:dyDescent="0.2">
       <c r="A39" s="20"/>
       <c r="B39" s="20"/>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="D39" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="20"/>
       <c r="B40" s="20"/>
       <c r="C40" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D40" s="7"/>
     </row>
@@ -1479,17 +1486,17 @@
       <c r="A41" s="20"/>
       <c r="B41" s="20"/>
       <c r="C41" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D41" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="20"/>
       <c r="B42" s="20"/>
       <c r="C42" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D42" s="9"/>
     </row>
@@ -1497,17 +1504,17 @@
       <c r="A43" s="20"/>
       <c r="B43" s="20"/>
       <c r="C43" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D43" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="20"/>
       <c r="B44" s="20"/>
       <c r="C44" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D44" s="11"/>
     </row>
@@ -1515,17 +1522,17 @@
       <c r="A45" s="20"/>
       <c r="B45" s="20"/>
       <c r="C45" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D45" s="5" t="s">
         <v>69</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="B46" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B46" s="23" t="s">
         <v>58</v>
       </c>
       <c r="C46" s="3" t="s">
@@ -1537,17 +1544,17 @@
       <c r="A47" s="20"/>
       <c r="B47" s="20"/>
       <c r="C47" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D47" s="5" t="s">
         <v>72</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="20"/>
       <c r="B48" s="20"/>
       <c r="C48" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D48" s="7"/>
     </row>
@@ -1555,17 +1562,17 @@
       <c r="A49" s="20"/>
       <c r="B49" s="20"/>
       <c r="C49" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D49" s="5" t="s">
         <v>74</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="20"/>
       <c r="B50" s="20"/>
       <c r="C50" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D50" s="9"/>
     </row>
@@ -1573,17 +1580,17 @@
       <c r="A51" s="20"/>
       <c r="B51" s="20"/>
       <c r="C51" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D51" s="5" t="s">
         <v>76</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="20"/>
       <c r="B52" s="20"/>
       <c r="C52" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D52" s="11"/>
     </row>
@@ -1591,15 +1598,15 @@
       <c r="A53" s="20"/>
       <c r="B53" s="20"/>
       <c r="C53" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D53" s="5" t="s">
         <v>78</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B55" s="20"/>
       <c r="C55" s="20"/>
@@ -1607,66 +1614,71 @@
     </row>
     <row r="56" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B56" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="B56" s="13" t="s">
+      <c r="C56" s="19" t="s">
         <v>82</v>
-      </c>
-      <c r="C56" s="19" t="s">
-        <v>83</v>
       </c>
       <c r="D56" s="20"/>
     </row>
     <row r="57" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B57" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="B57" s="13" t="s">
+      <c r="C57" s="19" t="s">
         <v>85</v>
-      </c>
-      <c r="C57" s="19" t="s">
-        <v>86</v>
       </c>
       <c r="D57" s="20"/>
     </row>
     <row r="58" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B58" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="B58" s="13" t="s">
+      <c r="C58" s="19" t="s">
         <v>88</v>
-      </c>
-      <c r="C58" s="19" t="s">
-        <v>89</v>
       </c>
       <c r="D58" s="20"/>
     </row>
     <row r="59" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B59" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="B59" s="13" t="s">
+      <c r="C59" s="19" t="s">
         <v>91</v>
-      </c>
-      <c r="C59" s="19" t="s">
-        <v>92</v>
       </c>
       <c r="D59" s="20"/>
     </row>
     <row r="60" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B60" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="B60" s="13" t="s">
+      <c r="C60" s="19" t="s">
         <v>94</v>
-      </c>
-      <c r="C60" s="19" t="s">
-        <v>95</v>
       </c>
       <c r="D60" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A30:A37"/>
+    <mergeCell ref="B46:B53"/>
+    <mergeCell ref="A6:A13"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="B14:B21"/>
     <mergeCell ref="C59:D59"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C60:D60"/>
@@ -1683,11 +1695,6 @@
     <mergeCell ref="A22:A29"/>
     <mergeCell ref="C58:D58"/>
     <mergeCell ref="B22:B29"/>
-    <mergeCell ref="A30:A37"/>
-    <mergeCell ref="B46:B53"/>
-    <mergeCell ref="A6:A13"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="B14:B21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1705,8 +1712,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="23" t="s">
-        <v>96</v>
+      <c r="A1" s="21" t="s">
+        <v>95</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -1714,7 +1721,7 @@
     </row>
     <row r="2" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -1722,7 +1729,7 @@
     </row>
     <row r="3" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="27" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B3" s="20"/>
       <c r="C3" s="20"/>
@@ -1734,13 +1741,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -1795,7 +1802,7 @@
     </row>
     <row r="11" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B11" s="2">
         <v>10</v>
@@ -1805,7 +1812,7 @@
     </row>
     <row r="12" spans="1:4" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B12" s="1">
         <v>100</v>
@@ -1818,7 +1825,7 @@
     </row>
     <row r="14" spans="1:4" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B14" s="29" t="str">
         <f>IF(C12&gt;=90,"A",IF(C12&gt;=80,"B",IF(C12&gt;=70,"C",IF(C12&gt;=60,"D","F"))))</f>
@@ -1828,7 +1835,7 @@
     </row>
     <row r="16" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B16" s="20"/>
       <c r="C16" s="20"/>
@@ -1836,55 +1843,55 @@
     </row>
     <row r="17" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="C17" s="19" t="s">
         <v>106</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>107</v>
       </c>
       <c r="D17" s="20"/>
     </row>
     <row r="18" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="B18" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="C18" s="19" t="s">
         <v>109</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>110</v>
       </c>
       <c r="D18" s="20"/>
     </row>
     <row r="19" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="B19" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="B19" s="18" t="s">
-        <v>112</v>
-      </c>
       <c r="C19" s="19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D19" s="20"/>
     </row>
     <row r="20" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="B20" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="C20" s="19" t="s">
         <v>114</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>115</v>
       </c>
       <c r="D20" s="20"/>
     </row>
     <row r="22" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B22" s="28"/>
       <c r="C22" s="20"/>

--- a/group-project/group-project-rubric.xlsx
+++ b/group-project/group-project-rubric.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/T7/Dropbox/LBS/01_websites_github_repos/e628-shared/group-project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{160B0ED0-4156-B14B-9AD1-9D699EDB4155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D175E96A-AAAC-6B40-8580-6B5F8E39D191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="67200" windowHeight="35520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D46" s="4"/>
     </row>
-    <row r="47" spans="1:4" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" ht="128" x14ac:dyDescent="0.2">
       <c r="A47" s="20"/>
       <c r="B47" s="20"/>
       <c r="C47" s="5" t="s">
